--- a/video-engine/sources/p10-rental-property/capture/states/p10_after.xlsx
+++ b/video-engine/sources/p10-rental-property/capture/states/p10_after.xlsx
@@ -3275,21 +3275,21 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
